--- a/document/TaskMan_タスク登録機能_画面設計書.xlsx
+++ b/document/TaskMan_タスク登録機能_画面設計書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER122\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6FB85A-5332-4C8C-8F07-108AF5533BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058CCD96-B7DD-4D6D-8047-63A8DDE11B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A8D82122-E492-4A39-81F9-E196E6F9C893}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="75">
   <si>
     <t>画面設計書</t>
   </si>
@@ -132,10 +132,6 @@
     <rPh sb="7" eb="9">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>task-add-success.jsp,TaskAddServlet.java,menu.jsp</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -230,10 +226,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>テキストボックス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>taskName</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -252,10 +244,6 @@
     <rPh sb="4" eb="5">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>セレクトボックス</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -311,10 +299,6 @@
     <rPh sb="0" eb="3">
       <t>タントウシャ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>LimitDate</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -495,6 +479,26 @@
     <t>menu.jsp</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>task-add-servlet,menu.jsp</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>text</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>select</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>submit</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>limitDate</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -1015,7 +1019,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1029,27 +1039,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1077,6 +1066,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1120,16 +1112,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3311,19 +3315,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3335,203 +3339,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42" t="s">
+      <c r="E2" s="39"/>
+      <c r="F2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="47">
+      <c r="G2" s="39"/>
+      <c r="H2" s="41">
         <v>46178</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="24"/>
+      <c r="I2" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="25"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="30"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="32"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="36"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="32"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="36"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
     </row>
     <row r="13" spans="1:10" ht="165.75" customHeight="1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
@@ -3544,248 +3548,248 @@
       <c r="G16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
+      <c r="A17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="14"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="16"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
+      <c r="A18" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="14"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="16"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="H19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="14"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
+      <c r="A20" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="14"/>
+        <v>74</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="16"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
+      <c r="A21" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="14"/>
+        <v>51</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="16"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
+      <c r="A22" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="14"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="16"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
+      <c r="A23" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
       <c r="D23" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="14"/>
+        <v>35</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
+      <c r="A24" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
       <c r="D24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="14"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="16"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="14"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A26" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
+      <c r="A26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="19"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="45"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4766,6 +4770,27 @@
     <row r="1003" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -4782,27 +4807,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -4827,19 +4831,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
@@ -4851,204 +4855,204 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42" t="s">
+      <c r="E2" s="39"/>
+      <c r="F2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="47">
+      <c r="G2" s="39"/>
+      <c r="H2" s="41">
         <v>46178</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="24"/>
+      <c r="I2" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="25"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:16" ht="28.5" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="30"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:16" ht="21" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:16" ht="21" customHeight="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="1:16" ht="21" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" spans="1:16" ht="21" customHeight="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="32"/>
     </row>
     <row r="10" spans="1:16" ht="21" customHeight="1">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="36"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="32"/>
     </row>
     <row r="11" spans="1:16" ht="21" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="36"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
     </row>
     <row r="13" spans="1:16" ht="129.75" customHeight="1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36"/>
-      <c r="P13" s="48"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="14" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
@@ -5061,83 +5065,83 @@
       <c r="G16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
+      <c r="A17" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="14"/>
+      <c r="G17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="16"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
+      <c r="A18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="14"/>
+        <v>61</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="16"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="14"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A20" s="15"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="19"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="45"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6118,6 +6122,15 @@
     <row r="997" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -6134,15 +6147,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -6166,19 +6170,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
@@ -6190,203 +6194,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42" t="s">
+      <c r="E2" s="39"/>
+      <c r="F2" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="47">
+      <c r="G2" s="39"/>
+      <c r="H2" s="41">
         <v>46178</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="24"/>
+      <c r="I2" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="20"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="25"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="20"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="30"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="32"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="36"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="32"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="34"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="36"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
     </row>
     <row r="13" spans="1:10" ht="141" customHeight="1">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="14"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="5" t="s">
         <v>15</v>
       </c>
@@ -6399,71 +6403,71 @@
       <c r="G16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="14"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
+      <c r="A17" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="14"/>
+      <c r="G17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="16"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
+      <c r="A18" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
       <c r="D18" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="14"/>
+        <v>61</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="16"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="19"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7444,6 +7448,13 @@
     <row r="996" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -7460,13 +7471,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
